--- a/data/trans_orig/IP16B03-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IP16B03-Clase-trans_orig.xlsx
@@ -1488,7 +1488,7 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>532</t>
+          <t>551</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
@@ -1503,7 +1503,7 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>16,42%</t>
+          <t>17,0%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>2707</t>
+          <t>2688</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1621,7 +1621,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>83,58%</t>
+          <t>83,0%</t>
         </is>
       </c>
     </row>
@@ -2825,7 +2825,7 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>5386</t>
+          <t>5367</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
@@ -2840,7 +2840,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>60,05%</t>
+          <t>59,85%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -2860,7 +2860,7 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>12026</t>
+          <t>11317</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
@@ -2875,7 +2875,7 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>77,18%</t>
+          <t>72,63%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
@@ -2943,7 +2943,7 @@
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3582</t>
+          <t>3601</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2958,7 +2958,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>39,95%</t>
+          <t>40,15%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2978,7 +2978,7 @@
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>3556</t>
+          <t>4265</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2993,7 +2993,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>22,82%</t>
+          <t>27,37%</t>
         </is>
       </c>
     </row>
@@ -5425,7 +5425,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>3185</t>
+          <t>3655</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -5440,7 +5440,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>48,52%</t>
+          <t>55,68%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -5495,7 +5495,7 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>8205</t>
+          <t>8855</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
@@ -5510,7 +5510,7 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>69,84%</t>
+          <t>75,38%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
@@ -5543,7 +5543,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3379</t>
+          <t>2909</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5558,7 +5558,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>51,48%</t>
+          <t>44,32%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5613,7 +5613,7 @@
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>3542</t>
+          <t>2892</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5628,7 +5628,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>30,16%</t>
+          <t>24,62%</t>
         </is>
       </c>
     </row>
@@ -8130,7 +8130,7 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>6469</t>
+          <t>6125</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
@@ -8145,7 +8145,7 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>75,3%</t>
+          <t>71,31%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
@@ -8248,7 +8248,7 @@
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>2121</t>
+          <t>2465</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8263,7 +8263,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>24,7%</t>
+          <t>28,69%</t>
         </is>
       </c>
     </row>
